--- a/Yield/Yield_2025.xlsx
+++ b/Yield/Yield_2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8688"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8685"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Plot</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Total_sample_weight_g</t>
+  </si>
+  <si>
+    <t>Harvest_area_m2</t>
   </si>
 </sst>
 </file>
@@ -402,18 +405,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,8 +433,11 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -446,8 +453,11 @@
       <c r="E2" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -463,8 +473,11 @@
       <c r="E3" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -480,8 +493,11 @@
       <c r="E4" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -497,8 +513,11 @@
       <c r="E5" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -514,8 +533,11 @@
       <c r="E6" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -531,8 +553,11 @@
       <c r="E7" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -548,8 +573,11 @@
       <c r="E8" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -565,8 +593,11 @@
       <c r="E9" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -582,8 +613,11 @@
       <c r="E10" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -599,8 +633,11 @@
       <c r="E11" s="1">
         <v>45937</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -616,8 +653,11 @@
       <c r="E12" s="1">
         <v>45938</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -633,8 +673,11 @@
       <c r="E13" s="1">
         <v>45938</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -650,8 +693,11 @@
       <c r="E14" s="1">
         <v>45938</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -667,8 +713,11 @@
       <c r="E15" s="1">
         <v>45938</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -683,6 +732,9 @@
       </c>
       <c r="E16" s="1">
         <v>45938</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
